--- a/Schedule/BCIO-schedule-hierarchy.xlsx
+++ b/Schedule/BCIO-schedule-hierarchy.xlsx
@@ -2087,7 +2087,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>spécification d’intervalle de dose</t>
+          <t>dose range specification</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2122,7 +2122,7 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>b is a relational specifically dependent continuant = Def. b is a specifically dependent continuant and there are n &amp;gt; 1 independent continuants c1, … cn which are not spatial regions are such that for all 1  i &amp;lt; j  n, ci  and cj share no common parts, are such that for each 1  i  n, b s-depends_on ci at every time t during the course of b’s existence (axiom label in BFO2 Reference: [131-004])</t>
+          <t>b is a specifically dependent continuant = Def. b is a continuant &amp; there is some independent continuant c which is not a spatial region and which is such that b s-depends_on c at every time t during the course of b’s existence. (axiom label in BFO2 Reference: [050-003])</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A disposition that inheres in some extended organism.</t>
+          <t>A &lt;disposition&gt; that inheres in some extended organism.</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Un établissement de santé qui a pour fonction d'entreposer, préparer, distribuer et surveiller l'utilisation des médicaments parmi les patients d'une zone géographique donnée ou suivis dans une organisation de soin donnée.</t>
+          <t>A health care facility whose function is to store, prepare, dispense, and monitor the usage of pharmaceutical drugs among patients in a given area or encountered in a given health care provider organization.</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>organisation</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -5207,7 +5207,7 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>A &lt;bodily process&gt; that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>A mental process that has positive or negative valence.</t>
+          <t>A &lt;mental process&gt; that has positive or negative valence.</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
-          <t>enjoyment</t>
+          <t>Genuss</t>
         </is>
       </c>
       <c r="J221" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>An affective process that involves the experience of internal or external sensory stimuli.</t>
+          <t>An &lt;affective process&gt; that involves the experience of internal or external sensory stimuli.</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
